--- a/etf_holdings/2026-09-21_common_daily_changes_min2.xlsx
+++ b/etf_holdings/2026-09-21_common_daily_changes_min2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH3"/>
+  <dimension ref="A1:AR4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,150 +439,200 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>00991A_異動類型</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>00991A_調整方向</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>00991A_股票名稱_昨日</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>00991A_股票名稱_今日</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>00991A_權重_昨日</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>00991A_權重_今日</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>00991A_權重變化</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>00991A_股數_昨日</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>00991A_股數_今日</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>00991A_股數變化</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
           <t>00403A_異動類型</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>00403A_調整方向</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>00403A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>00403A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>00403A_權重_昨日</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>00403A_權重_今日</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>00403A_權重變化</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>00403A_股數_昨日</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>00403A_股數_今日</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>00403A_股數變化</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>00992A_異動類型</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>00992A_調整方向</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>00992A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>00992A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>00992A_權重_昨日</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>00992A_權重_今日</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>00992A_權重變化</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>00992A_股數_昨日</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>00992A_股數_今日</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>00992A_股數變化</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>00405A_異動類型</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>00405A_調整方向</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>00405A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>00405A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>00405A_權重_昨日</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>00405A_權重_今日</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>00405A_權重變化</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>00405A_股數_昨日</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>00405A_股數_今日</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>00405A_股數變化</t>
         </is>
@@ -591,12 +641,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>台達電子</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -604,7 +654,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00403A,00992A</t>
+          <t>00403A,00991A</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -614,43 +664,43 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>台達電子</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>台達電子</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.76%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2.57%</t>
+          <t>2.07%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>+2.07%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2307000</v>
+        <v>1000</v>
       </c>
       <c r="M2" t="n">
-        <v>2180000</v>
+        <v>871000</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>-127,000</t>
+          <t>870,000</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -665,38 +715,38 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>4.88%</t>
+          <t>3.08%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>4.95%</t>
+          <t>3.40%</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>1074000</v>
+        <v>2750000</v>
       </c>
       <c r="W2" t="n">
-        <v>1104000</v>
+        <v>2830000</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>30,000</t>
+          <t>80,000</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr"/>
@@ -709,16 +759,26 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -726,107 +786,249 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>00403A,00992A</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>2.76%</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>2.57%</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>-0.19%</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>2307000</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2180000</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>-127,000</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>4.88%</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>4.95%</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>+0.07%</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>1074000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1104000</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>30,000</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>6805</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>00403A,00405A</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>富世達</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>富世達</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>1.13%</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>1.30%</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>+0.17%</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="V4" t="n">
         <v>762000</v>
       </c>
-      <c r="M3" t="n">
+      <c r="W4" t="n">
         <v>840000</v>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>78,000</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr">
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AK4" t="inlineStr">
         <is>
           <t>富世達</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>富世達</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>2.28%</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>3.43%</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AO4" t="inlineStr">
         <is>
           <t>+1.15%</t>
         </is>
       </c>
-      <c r="AF3" t="n">
+      <c r="AP4" t="n">
         <v>271000</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AQ4" t="n">
         <v>391000</v>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AR4" t="inlineStr">
         <is>
           <t>120,000</t>
         </is>
